--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2653"/>
+  <dimension ref="A1:E2654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48635,6 +48635,23 @@
         <v>-0.5333333333333333</v>
       </c>
       <c r="E2653" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2654">
+      <c r="A2654" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B2654" t="inlineStr"/>
+      <c r="C2654" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D2654" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E2654" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48668,7 +48685,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-22 | Publication days: 1582</t>
+          <t>Coverage: 2018-12-18 to 2026-03-23 | Publication days: 1582</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2654"/>
+  <dimension ref="A1:E2655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48652,6 +48652,23 @@
         <v>-0.6333333333333333</v>
       </c>
       <c r="E2654" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2655">
+      <c r="A2655" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B2655" t="inlineStr"/>
+      <c r="C2655" t="n">
+        <v>-1.571428571428571</v>
+      </c>
+      <c r="D2655" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E2655" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48685,7 +48702,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-23 | Publication days: 1582</t>
+          <t>Coverage: 2018-12-18 to 2026-03-24 | Publication days: 1582</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2655"/>
+  <dimension ref="A1:E2656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48669,6 +48669,23 @@
         <v>-0.7333333333333333</v>
       </c>
       <c r="E2655" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B2656" t="inlineStr"/>
+      <c r="C2656" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D2656" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="E2656" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48702,7 +48719,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-24 | Publication days: 1582</t>
+          <t>Coverage: 2018-12-18 to 2026-03-25 | Publication days: 1582</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -48661,15 +48661,17 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="B2655" t="inlineStr"/>
+      <c r="B2655" t="n">
+        <v>0</v>
+      </c>
       <c r="C2655" t="n">
-        <v>-1.571428571428571</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D2655" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E2655" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2656">
@@ -48678,15 +48680,17 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="B2656" t="inlineStr"/>
+      <c r="B2656" t="n">
+        <v>0</v>
+      </c>
       <c r="C2656" t="n">
-        <v>-2</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D2656" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E2656" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -48719,7 +48723,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-25 | Publication days: 1582</t>
+          <t>Coverage: 2018-12-18 to 2026-03-25 | Publication days: 1584</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -48714,21 +48726,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Canada WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2018-12-18 to 2026-03-25 | Publication days: 1584</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -48736,22 +48748,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2656"/>
+  <dimension ref="A1:E2657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -48703,6 +48691,23 @@
       </c>
       <c r="E2656" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2657">
+      <c r="A2657" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B2657" t="inlineStr"/>
+      <c r="C2657" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="D2657" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E2657" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -48726,21 +48731,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Canada WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2018-12-18 to 2026-03-25 | Publication days: 1584</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2018-12-18 to 2026-03-26 | Publication days: 1584</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -48748,22 +48753,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -48731,21 +48743,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Canada WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2018-12-18 to 2026-03-26 | Publication days: 1584</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -48753,22 +48765,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -48743,21 +48731,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Canada WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2018-12-18 to 2026-03-26 | Publication days: 1584</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -48765,22 +48753,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2657"/>
+  <dimension ref="A1:E2658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -48711,14 +48699,33 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B2657" t="inlineStr"/>
+      <c r="B2657" t="n">
+        <v>-3</v>
+      </c>
       <c r="C2657" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D2657" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E2657" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2658">
+      <c r="A2658" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B2658" t="inlineStr"/>
+      <c r="C2658" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D2658" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E2658" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48743,21 +48750,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Canada WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2018-12-18 to 2026-03-26 | Publication days: 1584</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2018-12-18 to 2026-03-27 | Publication days: 1585</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -48765,22 +48772,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -48571,13 +48571,13 @@
         </is>
       </c>
       <c r="B2650" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2650" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D2650" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E2650" t="b">
         <v>1</v>
@@ -48593,10 +48593,10 @@
         <v>0</v>
       </c>
       <c r="C2651" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D2651" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E2651" t="b">
         <v>1</v>
@@ -48612,10 +48612,10 @@
         <v>-3</v>
       </c>
       <c r="C2652" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D2652" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E2652" t="b">
         <v>1</v>
@@ -48629,10 +48629,10 @@
       </c>
       <c r="B2653" t="inlineStr"/>
       <c r="C2653" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D2653" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E2653" t="b">
         <v>0</v>
@@ -48646,10 +48646,10 @@
       </c>
       <c r="B2654" t="inlineStr"/>
       <c r="C2654" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D2654" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E2654" t="b">
         <v>0</v>
@@ -48665,10 +48665,10 @@
         <v>0</v>
       </c>
       <c r="C2655" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D2655" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E2655" t="b">
         <v>1</v>
@@ -48684,10 +48684,10 @@
         <v>0</v>
       </c>
       <c r="C2656" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D2656" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E2656" t="b">
         <v>1</v>
@@ -48706,7 +48706,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D2657" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E2657" t="b">
         <v>1</v>
@@ -48718,15 +48718,17 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B2658" t="inlineStr"/>
+      <c r="B2658" t="n">
+        <v>0</v>
+      </c>
       <c r="C2658" t="n">
-        <v>-2.142857142857143</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D2658" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6</v>
       </c>
       <c r="E2658" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -48759,7 +48761,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-27 | Publication days: 1585</t>
+          <t>Coverage: 2018-12-18 to 2026-03-27 | Publication days: 1586</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2658"/>
+  <dimension ref="A1:E2659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48571,13 +48571,13 @@
         </is>
       </c>
       <c r="B2650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2650" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D2650" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E2650" t="b">
         <v>1</v>
@@ -48593,10 +48593,10 @@
         <v>0</v>
       </c>
       <c r="C2651" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D2651" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E2651" t="b">
         <v>1</v>
@@ -48612,10 +48612,10 @@
         <v>-3</v>
       </c>
       <c r="C2652" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D2652" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E2652" t="b">
         <v>1</v>
@@ -48629,10 +48629,10 @@
       </c>
       <c r="B2653" t="inlineStr"/>
       <c r="C2653" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D2653" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E2653" t="b">
         <v>0</v>
@@ -48646,10 +48646,10 @@
       </c>
       <c r="B2654" t="inlineStr"/>
       <c r="C2654" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D2654" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E2654" t="b">
         <v>0</v>
@@ -48665,10 +48665,10 @@
         <v>0</v>
       </c>
       <c r="C2655" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D2655" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E2655" t="b">
         <v>1</v>
@@ -48684,10 +48684,10 @@
         <v>0</v>
       </c>
       <c r="C2656" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D2656" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E2656" t="b">
         <v>1</v>
@@ -48706,7 +48706,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D2657" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E2657" t="b">
         <v>1</v>
@@ -48725,10 +48725,27 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D2658" t="n">
-        <v>-0.6</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E2658" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2659">
+      <c r="A2659" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B2659" t="inlineStr"/>
+      <c r="C2659" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="D2659" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E2659" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -48761,7 +48778,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-27 | Publication days: 1586</t>
+          <t>Coverage: 2018-12-18 to 2026-03-28 | Publication days: 1586</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2659"/>
+  <dimension ref="A1:E2660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48746,6 +48746,25 @@
       </c>
       <c r="E2659" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2660">
+      <c r="A2660" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B2660" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2660" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D2660" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E2660" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -48778,7 +48797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-28 | Publication days: 1586</t>
+          <t>Coverage: 2018-12-18 to 2026-03-29 | Publication days: 1587</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2660"/>
+  <dimension ref="A1:E2661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48765,6 +48765,23 @@
       </c>
       <c r="E2660" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2661">
+      <c r="A2661" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B2661" t="inlineStr"/>
+      <c r="C2661" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D2661" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E2661" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -48797,7 +48814,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-29 | Publication days: 1587</t>
+          <t>Coverage: 2018-12-18 to 2026-03-30 | Publication days: 1587</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2661"/>
+  <dimension ref="A1:E2662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48773,7 +48773,9 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="B2661" t="inlineStr"/>
+      <c r="B2661" t="n">
+        <v>0</v>
+      </c>
       <c r="C2661" t="n">
         <v>-0.4285714285714285</v>
       </c>
@@ -48781,6 +48783,23 @@
         <v>-0.4333333333333333</v>
       </c>
       <c r="E2661" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2662">
+      <c r="A2662" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B2662" t="inlineStr"/>
+      <c r="C2662" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D2662" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E2662" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48814,7 +48833,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-30 | Publication days: 1587</t>
+          <t>Coverage: 2018-12-18 to 2026-03-31 | Publication days: 1588</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2662"/>
+  <dimension ref="A1:E2663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48800,6 +48800,23 @@
         <v>-0.4333333333333333</v>
       </c>
       <c r="E2662" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2663">
+      <c r="A2663" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B2663" t="inlineStr"/>
+      <c r="C2663" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D2663" t="n">
+        <v>-0.3666666666666666</v>
+      </c>
+      <c r="E2663" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48833,7 +48850,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-03-31 | Publication days: 1588</t>
+          <t>Coverage: 2018-12-18 to 2026-04-01 | Publication days: 1588</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2663"/>
+  <dimension ref="A1:E2664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48818,6 +48818,25 @@
       </c>
       <c r="E2663" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2664">
+      <c r="A2664" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B2664" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2664" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2664" t="n">
+        <v>-0.3666666666666666</v>
+      </c>
+      <c r="E2664" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -48850,7 +48869,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-01 | Publication days: 1588</t>
+          <t>Coverage: 2018-12-18 to 2026-04-02 | Publication days: 1589</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2664"/>
+  <dimension ref="A1:E2665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48836,6 +48836,25 @@
         <v>-0.3666666666666666</v>
       </c>
       <c r="E2664" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2665">
+      <c r="A2665" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B2665" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C2665" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D2665" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E2665" t="b">
         <v>1</v>
       </c>
     </row>
@@ -48869,7 +48888,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-02 | Publication days: 1589</t>
+          <t>Coverage: 2018-12-18 to 2026-04-03 | Publication days: 1590</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2665"/>
+  <dimension ref="A1:E2666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48856,6 +48856,23 @@
       </c>
       <c r="E2665" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2666">
+      <c r="A2666" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B2666" t="inlineStr"/>
+      <c r="C2666" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D2666" t="n">
+        <v>-0.5666666666666667</v>
+      </c>
+      <c r="E2666" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -48888,7 +48905,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-03 | Publication days: 1590</t>
+          <t>Coverage: 2018-12-18 to 2026-04-04 | Publication days: 1590</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2666"/>
+  <dimension ref="A1:E2667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48864,14 +48864,33 @@
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="B2666" t="inlineStr"/>
+      <c r="B2666" t="n">
+        <v>0</v>
+      </c>
       <c r="C2666" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D2666" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E2666" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2667">
+      <c r="A2667" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B2667" t="inlineStr"/>
+      <c r="C2667" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D2667" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E2667" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48905,7 +48924,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-04 | Publication days: 1590</t>
+          <t>Coverage: 2018-12-18 to 2026-04-05 | Publication days: 1591</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2667"/>
+  <dimension ref="A1:E2668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48891,6 +48891,23 @@
         <v>-0.4666666666666667</v>
       </c>
       <c r="E2667" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B2668" t="inlineStr"/>
+      <c r="C2668" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D2668" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E2668" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48924,7 +48941,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-05 | Publication days: 1591</t>
+          <t>Coverage: 2018-12-18 to 2026-04-06 | Publication days: 1591</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2668"/>
+  <dimension ref="A1:E2669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48908,6 +48908,23 @@
         <v>-0.4666666666666667</v>
       </c>
       <c r="E2668" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2669">
+      <c r="A2669" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B2669" t="inlineStr"/>
+      <c r="C2669" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D2669" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E2669" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48941,7 +48958,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-06 | Publication days: 1591</t>
+          <t>Coverage: 2018-12-18 to 2026-04-07 | Publication days: 1591</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2669"/>
+  <dimension ref="A1:E2670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48925,6 +48925,23 @@
         <v>-0.4666666666666667</v>
       </c>
       <c r="E2669" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2670">
+      <c r="A2670" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B2670" t="inlineStr"/>
+      <c r="C2670" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D2670" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E2670" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48958,7 +48975,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-07 | Publication days: 1591</t>
+          <t>Coverage: 2018-12-18 to 2026-04-08 | Publication days: 1591</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2670"/>
+  <dimension ref="A1:E2671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48942,6 +48942,23 @@
         <v>-0.4666666666666667</v>
       </c>
       <c r="E2670" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B2671" t="inlineStr"/>
+      <c r="C2671" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D2671" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E2671" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48975,7 +48992,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-08 | Publication days: 1591</t>
+          <t>Coverage: 2018-12-18 to 2026-04-09 | Publication days: 1591</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2671"/>
+  <dimension ref="A1:E2672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48951,15 +48951,36 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="B2671" t="inlineStr"/>
+      <c r="B2671" t="n">
+        <v>2</v>
+      </c>
       <c r="C2671" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D2671" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E2671" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2672">
+      <c r="A2672" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B2672" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2672" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D2672" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E2672" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -48992,7 +49013,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-09 | Publication days: 1591</t>
+          <t>Coverage: 2018-12-18 to 2026-04-10 | Publication days: 1593</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2672"/>
+  <dimension ref="A1:E2673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48981,6 +48981,23 @@
       </c>
       <c r="E2672" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2673">
+      <c r="A2673" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B2673" t="inlineStr"/>
+      <c r="C2673" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D2673" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E2673" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -49013,7 +49030,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-10 | Publication days: 1593</t>
+          <t>Coverage: 2018-12-18 to 2026-04-11 | Publication days: 1593</t>
         </is>
       </c>
     </row>

--- a/data/CA.xlsx
+++ b/data/CA.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2673"/>
+  <dimension ref="A1:E2674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48997,6 +48997,23 @@
         <v>-0.4</v>
       </c>
       <c r="E2673" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2674">
+      <c r="A2674" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B2674" t="inlineStr"/>
+      <c r="C2674" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D2674" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E2674" t="b">
         <v>0</v>
       </c>
     </row>
@@ -49030,7 +49047,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2018-12-18 to 2026-04-11 | Publication days: 1593</t>
+          <t>Coverage: 2018-12-18 to 2026-04-12 | Publication days: 1593</t>
         </is>
       </c>
     </row>
